--- a/data/fmsForecastOutput/File1/RPT_RPT7043243328387RJ_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT7043243328387RJ_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>364.2184972485598</v>
+        <v>364.2184972485597</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>387.2779454412351</v>
+        <v>387.2779454412349</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>481.2433810223013</v>
+        <v>481.2433810223011</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>465.8697956238066</v>
+        <v>465.8697956238064</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>454.3688268873256</v>
+        <v>454.3688268873254</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>364.2184972485598</v>
+        <v>364.2184972485597</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>387.2779454412351</v>
+        <v>387.2779454412349</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>481.2433810223013</v>
+        <v>481.2433810223011</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>465.8697956238066</v>
+        <v>465.8697956238064</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>454.3688268873256</v>
+        <v>454.3688268873254</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>47045.0215921963</v>
+        <v>47045.02159219629</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>36789.21074430101</v>
+        <v>36789.21074430099</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>28263.78239847889</v>
+        <v>28263.78239847888</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>26219.69839032407</v>
+        <v>26219.69839032406</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>26419.77349997146</v>
+        <v>26419.77349997144</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1928,46 +1928,46 @@
         <v>338.0862283876766</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>359.4911870239268</v>
+        <v>359.4911870239266</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>446.7147079444681</v>
+        <v>446.7147079444679</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>432.4441600633542</v>
+        <v>432.4441600633539</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>421.7683729402528</v>
+        <v>421.7683729402527</v>
       </c>
       <c r="Y8" s="148" t="n">
         <v>338.0862283876766</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>359.4911870239268</v>
+        <v>359.4911870239266</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>446.7147079444681</v>
+        <v>446.7147079444679</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>432.4441600633542</v>
+        <v>432.4441600633539</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>421.7683729402528</v>
+        <v>421.7683729402527</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>47045.0215921963</v>
+        <v>47045.02159219629</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>36789.21074430101</v>
+        <v>36789.21074430099</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>28263.78239847889</v>
+        <v>28263.78239847888</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>26219.69839032407</v>
+        <v>26219.69839032406</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>26419.77349997146</v>
+        <v>26419.77349997144</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         <v>936.6295904912823</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>883.1288466851278</v>
+        <v>883.1288466851277</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>997.123408743635</v>
+        <v>997.1234087436347</v>
       </c>
       <c r="F9" s="156" t="n">
         <v>1057.450210981242</v>
@@ -2040,10 +2040,10 @@
         <v>936.6295904912823</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>883.1288466851278</v>
+        <v>883.1288466851277</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>997.123408743635</v>
+        <v>997.1234087436347</v>
       </c>
       <c r="K9" s="156" t="n">
         <v>1057.450210981242</v>
@@ -2055,16 +2055,16 @@
         <v>60120.11633089469</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>42691.38631060591</v>
+        <v>42691.3863106059</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>34573.69262877763</v>
+        <v>34573.69262877762</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>37476.24754127128</v>
+        <v>37476.24754127126</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>40740.64016530425</v>
+        <v>40740.64016530423</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2075,46 +2075,46 @@
         <v>939.2754367921051</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>885.6235609413005</v>
+        <v>885.6235609413003</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>999.9401415366962</v>
+        <v>999.9401415366958</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>1060.43735846989</v>
+        <v>1060.437358469889</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>1087.626385358827</v>
+        <v>1087.626385358826</v>
       </c>
       <c r="Y9" s="155" t="n">
         <v>939.2754367921051</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>885.6235609413005</v>
+        <v>885.6235609413003</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>999.9401415366962</v>
+        <v>999.9401415366958</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>1060.43735846989</v>
+        <v>1060.437358469889</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>1087.626385358827</v>
+        <v>1087.626385358826</v>
       </c>
       <c r="AD9" s="158" t="n">
         <v>60120.11633089469</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>42691.38631060591</v>
+        <v>42691.3863106059</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>34573.69262877763</v>
+        <v>34573.69262877762</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>37476.24754127128</v>
+        <v>37476.24754127126</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>40740.64016530425</v>
+        <v>40740.64016530423</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2173,46 +2173,46 @@
         <v>554.2410455523824</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>554.5078113043718</v>
+        <v>554.5078113043717</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>672.7480033938548</v>
+        <v>672.7480033938544</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>694.4504179191593</v>
+        <v>694.4504179191591</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>701.705807612324</v>
+        <v>701.7058076123237</v>
       </c>
       <c r="H10" s="161" t="n">
         <v>554.2410455523824</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>554.5078113043718</v>
+        <v>554.5078113043717</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>672.7480033938548</v>
+        <v>672.7480033938544</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>694.4504179191593</v>
+        <v>694.4504179191591</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>701.705807612324</v>
+        <v>701.7058076123237</v>
       </c>
       <c r="M10" s="164" t="n">
         <v>107165.137923091</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>79480.59705490693</v>
+        <v>79480.5970549069</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>62837.47502725653</v>
+        <v>62837.4750272565</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>63695.94593159535</v>
+        <v>63695.94593159532</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>67160.4136652757</v>
+        <v>67160.41366527567</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2223,46 +2223,46 @@
         <v>527.4968753679793</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>527.9637059491374</v>
+        <v>527.9637059491373</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>642.2073703692053</v>
+        <v>642.2073703692049</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>663.694554780303</v>
+        <v>663.6945547803026</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>670.941348874039</v>
+        <v>670.9413488740388</v>
       </c>
       <c r="Y10" s="161" t="n">
         <v>527.4968753679793</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>527.9637059491374</v>
+        <v>527.9637059491373</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>642.2073703692053</v>
+        <v>642.2073703692049</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>663.694554780303</v>
+        <v>663.6945547803026</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>670.941348874039</v>
+        <v>670.9413488740388</v>
       </c>
       <c r="AD10" s="164" t="n">
         <v>107165.137923091</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>79480.59705490693</v>
+        <v>79480.5970549069</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>62837.47502725653</v>
+        <v>62837.4750272565</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>63695.94593159535</v>
+        <v>63695.94593159532</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>67160.4136652757</v>
+        <v>67160.41366527567</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2318,13 +2318,13 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>928.7187504663011</v>
+        <v>928.7187504663013</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>962.1106034544977</v>
+        <v>962.1106034544979</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>1075.679826272039</v>
+        <v>1075.67982627204</v>
       </c>
       <c r="F11" s="156" t="n">
         <v>1125.484657071871</v>
@@ -2333,13 +2333,13 @@
         <v>1140.596401784373</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>928.7187504663011</v>
+        <v>928.7187504663013</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>962.1106034544977</v>
+        <v>962.1106034544979</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>1075.679826272039</v>
+        <v>1075.67982627204</v>
       </c>
       <c r="K11" s="156" t="n">
         <v>1125.484657071871</v>
@@ -2348,13 +2348,13 @@
         <v>1140.596401784373</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>73568.03863341091</v>
+        <v>73568.03863341092</v>
       </c>
       <c r="N11" s="159" t="n">
         <v>73758.94372903106</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>78466.62670437836</v>
+        <v>78466.62670437837</v>
       </c>
       <c r="P11" s="159" t="n">
         <v>92328.07945432008</v>
@@ -2371,10 +2371,10 @@
         <v>1023.909182170166</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>1060.723583588382</v>
+        <v>1060.723583588383</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1185.933255511583</v>
+        <v>1185.933255511584</v>
       </c>
       <c r="W11" s="156" t="n">
         <v>1240.842907703675</v>
@@ -2386,10 +2386,10 @@
         <v>1023.909182170166</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>1060.723583588382</v>
+        <v>1060.723583588383</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>1185.933255511583</v>
+        <v>1185.933255511584</v>
       </c>
       <c r="AB11" s="156" t="n">
         <v>1240.842907703675</v>
@@ -2398,13 +2398,13 @@
         <v>1257.503553525646</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>73568.03863341091</v>
+        <v>73568.03863341092</v>
       </c>
       <c r="AE11" s="159" t="n">
         <v>73758.94372903106</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>78466.62670437836</v>
+        <v>78466.62670437837</v>
       </c>
       <c r="AG11" s="159" t="n">
         <v>92328.07945432008</v>
@@ -2464,31 +2464,31 @@
         <v>663.0723895950072</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>696.5462766183517</v>
+        <v>696.5462766183516</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>849.4372201500537</v>
+        <v>849.4372201500535</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>897.9519068353296</v>
+        <v>897.9519068353294</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>910.2024484420425</v>
+        <v>910.2024484420424</v>
       </c>
       <c r="H12" s="161" t="n">
         <v>663.0723895950072</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>696.5462766183517</v>
+        <v>696.5462766183516</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>849.4372201500537</v>
+        <v>849.4372201500535</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>897.9519068353296</v>
+        <v>897.9519068353294</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>910.2024484420425</v>
+        <v>910.2024484420424</v>
       </c>
       <c r="M12" s="164" t="n">
         <v>180733.1765565019</v>
@@ -2514,31 +2514,31 @@
         <v>657.1923777363595</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>696.2957908100148</v>
+        <v>696.2957908100146</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>861.555025061308</v>
+        <v>861.5550250613078</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>915.7450547498496</v>
+        <v>915.7450547498493</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>928.8675257166366</v>
+        <v>928.8675257166365</v>
       </c>
       <c r="Y12" s="161" t="n">
         <v>657.1923777363595</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>696.2957908100148</v>
+        <v>696.2957908100146</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>861.555025061308</v>
+        <v>861.5550250613078</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>915.7450547498496</v>
+        <v>915.7450547498493</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>928.8675257166366</v>
+        <v>928.8675257166365</v>
       </c>
       <c r="AD12" s="164" t="n">
         <v>180733.1765565019</v>
@@ -2606,46 +2606,46 @@
         <v>3010.375343991182</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>3121.147162621986</v>
+        <v>3121.147162621985</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>3306.861072216793</v>
+        <v>3306.861072216792</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>3463.76811366028</v>
+        <v>3463.768113660278</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>3655.256336241925</v>
+        <v>3655.256336241923</v>
       </c>
       <c r="H13" s="155" t="n">
         <v>3010.375343991182</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>3121.147162621986</v>
+        <v>3121.147162621985</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>3306.861072216793</v>
+        <v>3306.861072216792</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>3463.76811366028</v>
+        <v>3463.768113660278</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>3655.256336241925</v>
+        <v>3655.256336241923</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>9338.202013880056</v>
+        <v>9338.202013880054</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>9912.166698132292</v>
+        <v>9912.166698132289</v>
       </c>
       <c r="O13" s="159" t="n">
         <v>10808.98361690807</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>11550.21106054366</v>
+        <v>11550.21106054365</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>12434.57634387656</v>
+        <v>12434.57634387655</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>826.0176248756293</v>
+        <v>826.0176248756291</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>856.4123312072522</v>
+        <v>856.412331207252</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>907.3704161570466</v>
+        <v>907.3704161570464</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>950.4241775287351</v>
+        <v>950.4241775287346</v>
       </c>
       <c r="X13" s="157" t="n">
         <v>1002.966677627357</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>826.0176248756293</v>
+        <v>826.0176248756291</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>856.4123312072522</v>
+        <v>856.412331207252</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>907.3704161570466</v>
+        <v>907.3704161570464</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>950.4241775287351</v>
+        <v>950.4241775287346</v>
       </c>
       <c r="AC13" s="157" t="n">
         <v>1002.966677627357</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>9338.202013880056</v>
+        <v>9338.202013880054</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>9912.166698132292</v>
+        <v>9912.166698132289</v>
       </c>
       <c r="AF13" s="159" t="n">
         <v>10808.98361690807</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>11550.21106054366</v>
+        <v>11550.21106054365</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>12434.57634387656</v>
+        <v>12434.57634387655</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2755,10 +2755,10 @@
         <v>896.7931864434515</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>946.2658603302758</v>
+        <v>946.2658603302755</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>960.4820765305918</v>
+        <v>960.4820765305917</v>
       </c>
       <c r="H14" s="167" t="n">
         <v>689.4855397090854</v>
@@ -2770,10 +2770,10 @@
         <v>896.7931864434515</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>946.2658603302758</v>
+        <v>946.2658603302755</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>960.4820765305918</v>
+        <v>960.4820765305917</v>
       </c>
       <c r="M14" s="170" t="n">
         <v>190071.378570382</v>
@@ -2788,7 +2788,7 @@
         <v>167574.2364464591</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>178386.1930362548</v>
+        <v>178386.1930362547</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2805,10 +2805,10 @@
         <v>864.6573630442904</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>918.053935460073</v>
+        <v>918.0539354600727</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>933.6758373671204</v>
+        <v>933.6758373671203</v>
       </c>
       <c r="Y14" s="167" t="n">
         <v>663.8584514043145</v>
@@ -2820,10 +2820,10 @@
         <v>864.6573630442904</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>918.053935460073</v>
+        <v>918.0539354600727</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>933.6758373671204</v>
+        <v>933.6758373671203</v>
       </c>
       <c r="AD14" s="170" t="n">
         <v>190071.378570382</v>
@@ -2838,7 +2838,7 @@
         <v>167574.2364464591</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>178386.1930362548</v>
+        <v>178386.1930362547</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>79.21455079535443</v>
       </c>
       <c r="D22" s="80" t="n">
-        <v>76.66368447057597</v>
+        <v>76.66368447057596</v>
       </c>
       <c r="E22" s="80" t="n">
         <v>72.94608003974422</v>
@@ -3599,7 +3599,7 @@
         <v>79.21455079535443</v>
       </c>
       <c r="N22" s="80" t="n">
-        <v>76.66368447057597</v>
+        <v>76.66368447057596</v>
       </c>
       <c r="O22" s="80" t="n">
         <v>72.94608003974422</v>
@@ -3619,7 +3619,7 @@
         <v>71.85016006740376</v>
       </c>
       <c r="U22" s="80" t="n">
-        <v>69.53644179335365</v>
+        <v>69.53644179335363</v>
       </c>
       <c r="V22" s="80" t="n">
         <v>66.1644543145303</v>
@@ -3649,7 +3649,7 @@
         <v>71.85016006740376</v>
       </c>
       <c r="AE22" s="80" t="n">
-        <v>69.53644179335365</v>
+        <v>69.53644179335363</v>
       </c>
       <c r="AF22" s="80" t="n">
         <v>66.1644543145303</v>
@@ -4001,7 +4001,7 @@
         <v>175.9229630717332</v>
       </c>
       <c r="W25" s="92" t="n">
-        <v>182.5320168825168</v>
+        <v>182.5320168825169</v>
       </c>
       <c r="X25" s="93" t="n">
         <v>191.0579516969051</v>
@@ -4031,7 +4031,7 @@
         <v>175.9229630717332</v>
       </c>
       <c r="AG25" s="92" t="n">
-        <v>182.5320168825168</v>
+        <v>182.5320168825169</v>
       </c>
       <c r="AH25" s="93" t="n">
         <v>191.0579516969051</v>
@@ -4411,46 +4411,46 @@
         <v>370.9507945081133</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>404.7912747977797</v>
+        <v>404.7912747977795</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>506.6255294970563</v>
+        <v>506.625529497056</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>496.9178727528367</v>
+        <v>496.9178727528364</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>485.8455040695041</v>
+        <v>485.8455040695039</v>
       </c>
       <c r="H35" s="148" t="n">
         <v>370.9507945081133</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>404.7912747977797</v>
+        <v>404.7912747977795</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>506.6255294970563</v>
+        <v>506.625529497056</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>496.9178727528367</v>
+        <v>496.9178727528364</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>485.8455040695041</v>
+        <v>485.8455040695039</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>47914.61243487289</v>
+        <v>47914.61243487288</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>38452.87781369275</v>
+        <v>38452.87781369273</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>29754.49489362511</v>
+        <v>29754.4948936251</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>27967.12057903376</v>
+        <v>27967.12057903374</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>28250.01939818115</v>
+        <v>28250.01939818114</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4461,46 +4461,46 @@
         <v>344.3354908662756</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>375.7479546329166</v>
+        <v>375.7479546329163</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>470.2757157214828</v>
+        <v>470.2757157214825</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>461.2645724656376</v>
+        <v>461.2645724656374</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>450.9866338223648</v>
+        <v>450.9866338223646</v>
       </c>
       <c r="Y35" s="148" t="n">
         <v>344.3354908662756</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>375.7479546329166</v>
+        <v>375.7479546329163</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>470.2757157214828</v>
+        <v>470.2757157214825</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>461.2645724656376</v>
+        <v>461.2645724656374</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>450.9866338223648</v>
+        <v>450.9866338223646</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>47914.61243487289</v>
+        <v>47914.61243487288</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>38452.87781369275</v>
+        <v>38452.87781369273</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>29754.49489362511</v>
+        <v>29754.4948936251</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>27967.12057903376</v>
+        <v>27967.12057903374</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>28250.01939818115</v>
+        <v>28250.01939818114</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4513,10 +4513,10 @@
         <v>943.2290273246533</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>922.9150265861256</v>
+        <v>922.9150265861255</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>1048.602898161903</v>
+        <v>1048.602898161902</v>
       </c>
       <c r="F36" s="156" t="n">
         <v>1126.02765873116</v>
@@ -4528,10 +4528,10 @@
         <v>943.2290273246533</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>922.9150265861256</v>
+        <v>922.9150265861255</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>1048.602898161903</v>
+        <v>1048.602898161902</v>
       </c>
       <c r="K36" s="156" t="n">
         <v>1126.02765873116</v>
@@ -4543,16 +4543,16 @@
         <v>60543.71912346988</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>44614.69249899764</v>
+        <v>44614.69249899763</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>36358.66330364742</v>
+        <v>36358.66330364741</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>39906.6460422463</v>
+        <v>39906.64604224628</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>43490.15315934089</v>
+        <v>43490.15315934087</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>945.8935161024065</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>925.5221311810017</v>
+        <v>925.5221311810014</v>
       </c>
       <c r="V36" s="156" t="n">
         <v>1051.565053241456</v>
@@ -4572,13 +4572,13 @@
         <v>1129.208527823621</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1161.028346326243</v>
+        <v>1161.028346326242</v>
       </c>
       <c r="Y36" s="155" t="n">
         <v>945.8935161024065</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>925.5221311810017</v>
+        <v>925.5221311810014</v>
       </c>
       <c r="AA36" s="156" t="n">
         <v>1051.565053241456</v>
@@ -4587,22 +4587,22 @@
         <v>1129.208527823621</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>1161.028346326243</v>
+        <v>1161.028346326242</v>
       </c>
       <c r="AD36" s="158" t="n">
         <v>60543.71912346988</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>44614.69249899764</v>
+        <v>44614.69249899763</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>36358.66330364742</v>
+        <v>36358.66330364741</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>39906.6460422463</v>
+        <v>39906.64604224628</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>43490.15315934089</v>
+        <v>43490.15315934087</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4615,46 +4615,46 @@
         <v>560.9292373131957</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>579.5328458924585</v>
+        <v>579.5328458924582</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>707.8179884851278</v>
+        <v>707.8179884851274</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>739.999460036512</v>
+        <v>739.9994600365118</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>749.5560699434955</v>
+        <v>749.5560699434951</v>
       </c>
       <c r="H37" s="161" t="n">
         <v>560.9292373131957</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>579.5328458924585</v>
+        <v>579.5328458924582</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>707.8179884851278</v>
+        <v>707.8179884851274</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>739.999460036512</v>
+        <v>739.9994600365118</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>749.5560699434955</v>
+        <v>749.5560699434951</v>
       </c>
       <c r="M37" s="164" t="n">
         <v>108458.3315583428</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>83067.5703126904</v>
+        <v>83067.57031269037</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>66113.15819727254</v>
+        <v>66113.15819727251</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>67873.76662128005</v>
+        <v>67873.76662128002</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>71740.17255752203</v>
+        <v>71740.172557522</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4665,46 +4665,46 @@
         <v>533.8623372622254</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>551.7908004161246</v>
+        <v>551.7908004161245</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>675.6852889817236</v>
+        <v>675.6852889817233</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>707.2263180980187</v>
+        <v>707.2263180980184</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>716.6937414068793</v>
+        <v>716.6937414068791</v>
       </c>
       <c r="Y37" s="161" t="n">
         <v>533.8623372622254</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>551.7908004161246</v>
+        <v>551.7908004161245</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>675.6852889817236</v>
+        <v>675.6852889817233</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>707.2263180980187</v>
+        <v>707.2263180980184</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>716.6937414068793</v>
+        <v>716.6937414068791</v>
       </c>
       <c r="AD37" s="164" t="n">
         <v>108458.3315583428</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>83067.5703126904</v>
+        <v>83067.57031269037</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>66113.15819727254</v>
+        <v>66113.15819727251</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>67873.76662128005</v>
+        <v>67873.76662128002</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>71740.17255752203</v>
+        <v>71740.172557522</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>946.2541837967573</v>
+        <v>946.2541837967575</v>
       </c>
       <c r="D38" s="156" t="n">
         <v>1006.585188014542</v>
@@ -4729,7 +4729,7 @@
         <v>1216.277686158409</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>946.2541837967573</v>
+        <v>946.2541837967575</v>
       </c>
       <c r="I38" s="156" t="n">
         <v>1006.585188014542</v>
@@ -4744,13 +4744,13 @@
         <v>1216.277686158409</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>74957.10010768488</v>
+        <v>74957.10010768489</v>
       </c>
       <c r="N38" s="159" t="n">
         <v>77168.52924670224</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>82585.75668911457</v>
+        <v>82585.75668911458</v>
       </c>
       <c r="P38" s="159" t="n">
         <v>98340.03651065363</v>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>1043.241936237392</v>
+        <v>1043.241936237393</v>
       </c>
       <c r="U38" s="156" t="n">
         <v>1109.756657897875</v>
@@ -4779,7 +4779,7 @@
         <v>1340.941905502604</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>1043.241936237392</v>
+        <v>1043.241936237393</v>
       </c>
       <c r="Z38" s="156" t="n">
         <v>1109.756657897875</v>
@@ -4794,13 +4794,13 @@
         <v>1340.941905502604</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>74957.10010768488</v>
+        <v>74957.10010768489</v>
       </c>
       <c r="AE38" s="159" t="n">
         <v>77168.52924670224</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>82585.75668911457</v>
+        <v>82585.75668911458</v>
       </c>
       <c r="AG38" s="159" t="n">
         <v>98340.03651065363</v>
@@ -4819,31 +4819,31 @@
         <v>672.9130250492324</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>728.3489493440272</v>
+        <v>728.3489493440271</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>893.8904911643054</v>
+        <v>893.8904911643053</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>956.5962748077206</v>
+        <v>956.5962748077204</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>971.2739433169227</v>
+        <v>971.2739433169226</v>
       </c>
       <c r="H39" s="161" t="n">
         <v>672.9130250492324</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>728.3489493440272</v>
+        <v>728.3489493440271</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>893.8904911643054</v>
+        <v>893.8904911643053</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>956.5962748077206</v>
+        <v>956.5962748077204</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>971.2739433169227</v>
+        <v>971.2739433169226</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>183415.4316660276</v>
@@ -4855,7 +4855,7 @@
         <v>148698.9148863871</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>166213.8031319337</v>
+        <v>166213.8031319336</v>
       </c>
       <c r="Q39" s="166" t="n">
         <v>177086.406898287</v>
@@ -4869,31 +4869,31 @@
         <v>666.9457481286165</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>728.0870269399429</v>
+        <v>728.0870269399428</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>906.6424524947037</v>
+        <v>906.6424524947034</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>975.5514759522001</v>
+        <v>975.5514759521998</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>991.191383923505</v>
+        <v>991.1913839235049</v>
       </c>
       <c r="Y39" s="161" t="n">
         <v>666.9457481286165</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>728.0870269399429</v>
+        <v>728.0870269399428</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>906.6424524947037</v>
+        <v>906.6424524947034</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>975.5514759522001</v>
+        <v>975.5514759521998</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>991.191383923505</v>
+        <v>991.1913839235049</v>
       </c>
       <c r="AD39" s="164" t="n">
         <v>183415.4316660276</v>
@@ -4905,7 +4905,7 @@
         <v>148698.9148863871</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>166213.8031319337</v>
+        <v>166213.8031319336</v>
       </c>
       <c r="AH39" s="166" t="n">
         <v>177086.406898287</v>
@@ -4921,34 +4921,34 @@
         <v>3037.735167311229</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>3210.240228841176</v>
+        <v>3210.240228841175</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>3412.846786470453</v>
+        <v>3412.846786470452</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>3609.878029352035</v>
+        <v>3609.878029352033</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>3809.011307703917</v>
+        <v>3809.011307703916</v>
       </c>
       <c r="H40" s="155" t="n">
         <v>3037.735167311229</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>3210.240228841176</v>
+        <v>3210.240228841175</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>3412.846786470453</v>
+        <v>3412.846786470452</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>3609.878029352035</v>
+        <v>3609.878029352033</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>3809.011307703917</v>
+        <v>3809.011307703916</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>9423.072346656545</v>
+        <v>9423.072346656543</v>
       </c>
       <c r="N40" s="159" t="n">
         <v>10195.10924393346</v>
@@ -4968,37 +4968,37 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>833.5248934695446</v>
+        <v>833.5248934695444</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>880.8585993771519</v>
+        <v>880.8585993771517</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>936.4518621412827</v>
+        <v>936.4518621412825</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>990.5153129319606</v>
+        <v>990.5153129319601</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>1045.155541748026</v>
+        <v>1045.155541748025</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>833.5248934695446</v>
+        <v>833.5248934695444</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>880.8585993771519</v>
+        <v>880.8585993771517</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>936.4518621412827</v>
+        <v>936.4518621412825</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>990.5153129319606</v>
+        <v>990.5153129319601</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>1045.155541748026</v>
+        <v>1045.155541748025</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>9423.072346656545</v>
+        <v>9423.072346656543</v>
       </c>
       <c r="AE40" s="159" t="n">
         <v>10195.10924393346</v>
@@ -5023,13 +5023,13 @@
         <v>699.5233107474115</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>763.6665974343124</v>
+        <v>763.6665974343123</v>
       </c>
       <c r="E41" s="180" t="n">
         <v>942.4322229110438</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>1006.557192100652</v>
+        <v>1006.557192100651</v>
       </c>
       <c r="G41" s="181" t="n">
         <v>1023.251203190941</v>
@@ -5038,13 +5038,13 @@
         <v>699.5233107474115</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>763.6665974343124</v>
+        <v>763.6665974343123</v>
       </c>
       <c r="J41" s="180" t="n">
         <v>942.4322229110438</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>1006.557192100652</v>
+        <v>1006.557192100651</v>
       </c>
       <c r="L41" s="181" t="n">
         <v>1023.251203190941</v>
@@ -5062,7 +5062,7 @@
         <v>178251.2293607279</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>190044.0321763624</v>
+        <v>190044.0321763623</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5073,31 +5073,31 @@
         <v>673.52313435019</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>735.7199634554458</v>
+        <v>735.7199634554457</v>
       </c>
       <c r="V41" s="186" t="n">
         <v>908.6609633397514</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>976.5477443634223</v>
+        <v>976.5477443634219</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>994.693131002727</v>
+        <v>994.6931310027268</v>
       </c>
       <c r="Y41" s="185" t="n">
         <v>673.52313435019</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>735.7199634554458</v>
+        <v>735.7199634554457</v>
       </c>
       <c r="AA41" s="186" t="n">
         <v>908.6609633397514</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>976.5477443634223</v>
+        <v>976.5477443634219</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>994.693131002727</v>
+        <v>994.6931310027268</v>
       </c>
       <c r="AD41" s="188" t="n">
         <v>192838.5040126842</v>
@@ -5112,7 +5112,7 @@
         <v>178251.2293607279</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>190044.0321763624</v>
+        <v>190044.0321763623</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -6337,7 +6337,7 @@
         <v>0.5319689580550878</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.02764954899003751</v>
+        <v>0.0276495489900375</v>
       </c>
       <c r="E57" s="149" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
         <v>0.5319689580550878</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.02764954899003751</v>
+        <v>0.0276495489900375</v>
       </c>
       <c r="J57" s="149" t="n">
         <v>0</v>
@@ -6367,7 +6367,7 @@
         <v>68.71285041023197</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>2.626550509145154</v>
+        <v>2.626550509145153</v>
       </c>
       <c r="O57" s="152" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
         <v>0.4938007816923911</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.02566572484725455</v>
+        <v>0.02566572484725453</v>
       </c>
       <c r="V57" s="149" t="n">
         <v>0</v>
@@ -6402,7 +6402,7 @@
         <v>0.4938007816923911</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.02566572484725455</v>
+        <v>0.02566572484725453</v>
       </c>
       <c r="AA57" s="149" t="n">
         <v>0</v>
@@ -6417,7 +6417,7 @@
         <v>68.71285041023197</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>2.626550509145154</v>
+        <v>2.626550509145153</v>
       </c>
       <c r="AF57" s="152" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>8.977744936167248</v>
+        <v>8.977744936167246</v>
       </c>
       <c r="D58" s="156" t="n">
         <v>0.4900507240947733</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>8.977744936167248</v>
+        <v>8.977744936167246</v>
       </c>
       <c r="I58" s="156" t="n">
         <v>0.4900507240947733</v>
@@ -6466,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>576.2609631715445</v>
+        <v>576.2609631715444</v>
       </c>
       <c r="N58" s="159" t="n">
         <v>23.68957242496383</v>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>9.003105797568848</v>
+        <v>9.003105797568846</v>
       </c>
       <c r="U58" s="156" t="n">
         <v>0.4914350481741371</v>
@@ -6501,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>9.003105797568848</v>
+        <v>9.003105797568846</v>
       </c>
       <c r="Z58" s="156" t="n">
         <v>0.4914350481741371</v>
@@ -6516,7 +6516,7 @@
         <v>0</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>576.2609631715445</v>
+        <v>576.2609631715444</v>
       </c>
       <c r="AE58" s="159" t="n">
         <v>23.68957242496383</v>
@@ -6568,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>644.9738135817765</v>
+        <v>644.9738135817763</v>
       </c>
       <c r="N59" s="165" t="n">
         <v>26.31612293410899</v>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>3.174742065864021</v>
+        <v>3.17474206586402</v>
       </c>
       <c r="U59" s="162" t="n">
         <v>0.1748094290346991</v>
@@ -6603,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>3.174742065864021</v>
+        <v>3.17474206586402</v>
       </c>
       <c r="Z59" s="162" t="n">
         <v>0.1748094290346991</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>644.9738135817765</v>
+        <v>644.9738135817763</v>
       </c>
       <c r="AE59" s="165" t="n">
         <v>26.31612293410899</v>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>2.974796133805501</v>
+        <v>2.9747961338055</v>
       </c>
       <c r="D61" s="162" t="n">
         <v>0.1196192402496794</v>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>2.974796133805501</v>
+        <v>2.9747961338055</v>
       </c>
       <c r="I61" s="162" t="n">
         <v>0.1196192402496794</v>
@@ -6772,7 +6772,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>810.8380974799032</v>
+        <v>810.8380974799031</v>
       </c>
       <c r="N61" s="165" t="n">
         <v>26.31612293410899</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>2.948416153552487</v>
+        <v>2.948416153552486</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0.1195762238369982</v>
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>2.948416153552487</v>
+        <v>2.948416153552486</v>
       </c>
       <c r="Z61" s="162" t="n">
         <v>0.1195762238369982</v>
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>810.8380974799032</v>
+        <v>810.8380974799031</v>
       </c>
       <c r="AE61" s="165" t="n">
         <v>26.31612293410899</v>
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>810.8380974799032</v>
+        <v>810.8380974799031</v>
       </c>
       <c r="N63" s="183" t="n">
         <v>26.31612293410899</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>810.8380974799032</v>
+        <v>810.8380974799031</v>
       </c>
       <c r="AE63" s="189" t="n">
         <v>26.31612293410899</v>
@@ -7300,13 +7300,13 @@
         <v>1.242159160512869</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.7591585748340781</v>
+        <v>0.7591585748340774</v>
       </c>
       <c r="E68" s="149" t="n">
         <v>0.5613739761420932</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.2613110254668587</v>
+        <v>0.2613110254668586</v>
       </c>
       <c r="G68" s="150" t="n">
         <v>0.2776097372759249</v>
@@ -7315,13 +7315,13 @@
         <v>1.242159160512869</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.7591585748340781</v>
+        <v>0.7591585748340774</v>
       </c>
       <c r="J68" s="149" t="n">
         <v>0.5613739761420932</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.2613110254668587</v>
+        <v>0.2613110254668586</v>
       </c>
       <c r="L68" s="150" t="n">
         <v>0.2776097372759249</v>
@@ -7330,16 +7330,16 @@
         <v>160.4460096582956</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>72.11576369548776</v>
+        <v>72.1157636954877</v>
       </c>
       <c r="O68" s="152" t="n">
         <v>32.96991196459434</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>14.70689093426431</v>
+        <v>14.7068909342643</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>16.14192247839948</v>
+        <v>16.14192247839947</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>1.153035633301183</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.7046897981643684</v>
+        <v>0.7046897981643678</v>
       </c>
       <c r="V68" s="149" t="n">
         <v>0.5210960226969206</v>
@@ -7359,13 +7359,13 @@
         <v>0.2425622523391917</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.2576915498480559</v>
+        <v>0.2576915498480558</v>
       </c>
       <c r="Y68" s="148" t="n">
         <v>1.153035633301183</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.7046897981643684</v>
+        <v>0.7046897981643678</v>
       </c>
       <c r="AA68" s="149" t="n">
         <v>0.5210960226969206</v>
@@ -7374,22 +7374,22 @@
         <v>0.2425622523391917</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.2576915498480559</v>
+        <v>0.2576915498480558</v>
       </c>
       <c r="AD68" s="151" t="n">
         <v>160.4460096582956</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>72.11576369548776</v>
+        <v>72.1157636954877</v>
       </c>
       <c r="AF68" s="152" t="n">
         <v>32.96991196459434</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>14.70689093426431</v>
+        <v>14.7068909342643</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>16.14192247839948</v>
+        <v>16.14192247839947</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7399,13 +7399,13 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>6.191346922710103</v>
+        <v>6.191346922710101</v>
       </c>
       <c r="D69" s="156" t="n">
         <v>1.433935379831054</v>
       </c>
       <c r="E69" s="156" t="n">
-        <v>2.270717326691265</v>
+        <v>2.270717326691266</v>
       </c>
       <c r="F69" s="156" t="n">
         <v>2.466453757338032</v>
@@ -7414,13 +7414,13 @@
         <v>2.576551393678578</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>6.191346922710103</v>
+        <v>6.191346922710101</v>
       </c>
       <c r="I69" s="156" t="n">
         <v>1.433935379831054</v>
       </c>
       <c r="J69" s="156" t="n">
-        <v>2.270717326691265</v>
+        <v>2.270717326691266</v>
       </c>
       <c r="K69" s="156" t="n">
         <v>2.466453757338032</v>
@@ -7429,19 +7429,19 @@
         <v>2.576551393678578</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>397.4084323377169</v>
+        <v>397.4084323377168</v>
       </c>
       <c r="N69" s="159" t="n">
         <v>69.31795906632776</v>
       </c>
       <c r="O69" s="159" t="n">
-        <v>78.73356719082699</v>
+        <v>78.73356719082702</v>
       </c>
       <c r="P69" s="159" t="n">
         <v>87.41161578976542</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>96.78588257492848</v>
+        <v>96.78588257492851</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,49 +7449,49 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>6.208836603282729</v>
+        <v>6.208836603282728</v>
       </c>
       <c r="U69" s="156" t="n">
         <v>1.437986044745831</v>
       </c>
       <c r="V69" s="156" t="n">
-        <v>2.277131782416382</v>
+        <v>2.277131782416383</v>
       </c>
       <c r="W69" s="156" t="n">
         <v>2.473421140833338</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>2.583829787446031</v>
+        <v>2.583829787446032</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>6.208836603282729</v>
+        <v>6.208836603282728</v>
       </c>
       <c r="Z69" s="156" t="n">
         <v>1.437986044745831</v>
       </c>
       <c r="AA69" s="156" t="n">
-        <v>2.277131782416382</v>
+        <v>2.277131782416383</v>
       </c>
       <c r="AB69" s="156" t="n">
         <v>2.473421140833338</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>2.583829787446031</v>
+        <v>2.583829787446032</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>397.4084323377169</v>
+        <v>397.4084323377168</v>
       </c>
       <c r="AE69" s="159" t="n">
         <v>69.31795906632776</v>
       </c>
       <c r="AF69" s="159" t="n">
-        <v>78.73356719082699</v>
+        <v>78.73356719082702</v>
       </c>
       <c r="AG69" s="159" t="n">
         <v>87.41161578976542</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>96.78588257492848</v>
+        <v>96.78588257492851</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7504,34 +7504,34 @@
         <v>2.885134430749333</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.9867326990398068</v>
+        <v>0.9867326990398064</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>1.195915216856824</v>
+        <v>1.195915216856825</v>
       </c>
       <c r="F70" s="162" t="n">
         <v>1.113355624672591</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>1.179892920877042</v>
+        <v>1.179892920877043</v>
       </c>
       <c r="H70" s="161" t="n">
         <v>2.885134430749333</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.9867326990398068</v>
+        <v>0.9867326990398064</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>1.195915216856824</v>
+        <v>1.195915216856825</v>
       </c>
       <c r="K70" s="162" t="n">
         <v>1.113355624672591</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>1.179892920877042</v>
+        <v>1.179892920877043</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>557.8544419960125</v>
+        <v>557.8544419960124</v>
       </c>
       <c r="N70" s="165" t="n">
         <v>141.4337227618155</v>
@@ -7554,7 +7554,7 @@
         <v>2.745916076497096</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.9394981313983592</v>
+        <v>0.9394981313983589</v>
       </c>
       <c r="V70" s="162" t="n">
         <v>1.141624445895984</v>
@@ -7569,7 +7569,7 @@
         <v>2.745916076497096</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.9394981313983592</v>
+        <v>0.9394981313983589</v>
       </c>
       <c r="AA70" s="162" t="n">
         <v>1.141624445895984</v>
@@ -7581,7 +7581,7 @@
         <v>1.128163596869551</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>557.8544419960125</v>
+        <v>557.8544419960124</v>
       </c>
       <c r="AE70" s="165" t="n">
         <v>141.4337227618155</v>
@@ -7606,13 +7606,13 @@
         <v>2.016881338330298</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.9904335859030238</v>
+        <v>0.9904335859030239</v>
       </c>
       <c r="E71" s="156" t="n">
         <v>1.520086588818991</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>2.33229368725836</v>
+        <v>2.332293687258361</v>
       </c>
       <c r="G71" s="157" t="n">
         <v>3.988732239266056</v>
@@ -7621,13 +7621,13 @@
         <v>2.016881338330298</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.9904335859030238</v>
+        <v>0.9904335859030239</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>1.520086588818991</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>2.33229368725836</v>
+        <v>2.332293687258361</v>
       </c>
       <c r="L71" s="157" t="n">
         <v>3.988732239266056</v>
@@ -7642,7 +7642,7 @@
         <v>110.8843579753319</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>191.3275276699291</v>
+        <v>191.3275276699292</v>
       </c>
       <c r="Q71" s="160" t="n">
         <v>345.4786073791039</v>
@@ -7662,7 +7662,7 @@
         <v>1.675890160723062</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>2.571345653032554</v>
+        <v>2.571345653032555</v>
       </c>
       <c r="X71" s="157" t="n">
         <v>4.397563377451023</v>
@@ -7677,7 +7677,7 @@
         <v>1.675890160723062</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>2.571345653032554</v>
+        <v>2.571345653032555</v>
       </c>
       <c r="AC71" s="157" t="n">
         <v>4.397563377451023</v>
@@ -7692,7 +7692,7 @@
         <v>110.8843579753319</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>191.3275276699291</v>
+        <v>191.3275276699292</v>
       </c>
       <c r="AH71" s="160" t="n">
         <v>345.4786073791039</v>
@@ -7708,7 +7708,7 @@
         <v>2.632801248353735</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.9880223572572568</v>
+        <v>0.9880223572572566</v>
       </c>
       <c r="E72" s="162" t="n">
         <v>1.338067269771478</v>
@@ -7723,7 +7723,7 @@
         <v>2.632801248353735</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.9880223572572568</v>
+        <v>0.9880223572572566</v>
       </c>
       <c r="J72" s="162" t="n">
         <v>1.338067269771478</v>
@@ -7735,7 +7735,7 @@
         <v>2.514242688885448</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>717.6207912193803</v>
+        <v>717.6207912193802</v>
       </c>
       <c r="N72" s="165" t="n">
         <v>217.364010680546</v>
@@ -7744,7 +7744,7 @@
         <v>222.5878371307532</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>293.4460343939588</v>
+        <v>293.4460343939589</v>
       </c>
       <c r="Q72" s="166" t="n">
         <v>458.4064124324319</v>
@@ -7758,7 +7758,7 @@
         <v>2.60945401989918</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.9876670534000399</v>
+        <v>0.9876670534000397</v>
       </c>
       <c r="V72" s="162" t="n">
         <v>1.357155717685688</v>
@@ -7773,7 +7773,7 @@
         <v>2.60945401989918</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.9876670534000399</v>
+        <v>0.9876670534000397</v>
       </c>
       <c r="AA72" s="162" t="n">
         <v>1.357155717685688</v>
@@ -7785,7 +7785,7 @@
         <v>2.56580103632283</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>717.6207912193803</v>
+        <v>717.6207912193802</v>
       </c>
       <c r="AE72" s="165" t="n">
         <v>217.364010680546</v>
@@ -7794,7 +7794,7 @@
         <v>222.5878371307532</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>293.4460343939588</v>
+        <v>293.4460343939589</v>
       </c>
       <c r="AH72" s="166" t="n">
         <v>458.4064124324319</v>
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>43.91169408368145</v>
+        <v>43.91169408368143</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>58.39233312524617</v>
+        <v>58.39233312524614</v>
       </c>
       <c r="E73" s="156" t="n">
-        <v>72.19577991560118</v>
+        <v>72.19577991560115</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>85.70928655784053</v>
+        <v>85.7092865578405</v>
       </c>
       <c r="G73" s="157" t="n">
         <v>100.3205523725292</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>43.91169408368145</v>
+        <v>43.91169408368143</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>58.39233312524617</v>
+        <v>58.39233312524614</v>
       </c>
       <c r="J73" s="156" t="n">
-        <v>72.19577991560118</v>
+        <v>72.19577991560115</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>85.70928655784053</v>
+        <v>85.7092865578405</v>
       </c>
       <c r="L73" s="157" t="n">
         <v>100.3205523725292</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>136.2143331872573</v>
+        <v>136.2143331872572</v>
       </c>
       <c r="N73" s="159" t="n">
         <v>185.4428867570869</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>235.9830017880094</v>
+        <v>235.9830017880093</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>285.8044525808488</v>
+        <v>285.8044525808486</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>341.2738950665808</v>
+        <v>341.2738950665807</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7863,13 +7863,13 @@
         <v>16.02228652826876</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>19.80981765976862</v>
+        <v>19.8098176597686</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>23.5177920433099</v>
+        <v>23.51779204330989</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>27.5269808339257</v>
+        <v>27.52698083392569</v>
       </c>
       <c r="Y73" s="155" t="n">
         <v>12.04894044979064</v>
@@ -7878,28 +7878,28 @@
         <v>16.02228652826876</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>19.80981765976862</v>
+        <v>19.8098176597686</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>23.5177920433099</v>
+        <v>23.51779204330989</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>27.5269808339257</v>
+        <v>27.52698083392569</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>136.2143331872573</v>
+        <v>136.2143331872572</v>
       </c>
       <c r="AE73" s="159" t="n">
         <v>185.4428867570869</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>235.9830017880094</v>
+        <v>235.9830017880093</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>285.8044525808488</v>
+        <v>285.8044525808486</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>341.2738950665808</v>
+        <v>341.2738950665807</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7912,13 +7912,13 @@
         <v>3.097294163919008</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>1.804893452021717</v>
+        <v>1.804893452021716</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>2.703536010078985</v>
+        <v>2.703536010078984</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>3.270938134807356</v>
+        <v>3.270938134807353</v>
       </c>
       <c r="G74" s="181" t="n">
         <v>4.305706564135104</v>
@@ -7927,31 +7927,31 @@
         <v>3.097294163919008</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>1.804893452021717</v>
+        <v>1.804893452021716</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>2.703536010078985</v>
+        <v>2.703536010078984</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>3.270938134807356</v>
+        <v>3.270938134807353</v>
       </c>
       <c r="L74" s="181" t="n">
         <v>4.305706564135104</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>853.8351244066375</v>
+        <v>853.8351244066374</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>402.806897437633</v>
+        <v>402.8068974376328</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>458.5708389187627</v>
+        <v>458.5708389187625</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>579.2504869748077</v>
+        <v>579.2504869748075</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>799.6803074990127</v>
+        <v>799.6803074990125</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7962,46 +7962,46 @@
         <v>2.982172632758116</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>1.738842773827896</v>
+        <v>1.738842773827895</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>2.606657089624955</v>
+        <v>2.606657089624954</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>3.173418542499483</v>
+        <v>3.173418542499482</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>4.185537950116976</v>
+        <v>4.185537950116975</v>
       </c>
       <c r="Y74" s="185" t="n">
         <v>2.982172632758116</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>1.738842773827896</v>
+        <v>1.738842773827895</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>2.606657089624955</v>
+        <v>2.606657089624954</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>3.173418542499483</v>
+        <v>3.173418542499482</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>4.185537950116976</v>
+        <v>4.185537950116975</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>853.8351244066375</v>
+        <v>853.8351244066374</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>402.806897437633</v>
+        <v>402.8068974376328</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>458.5708389187627</v>
+        <v>458.5708389187625</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>579.2504869748077</v>
+        <v>579.2504869748075</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>799.6803074990127</v>
+        <v>799.6803074990125</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,49 +8260,49 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>372.7249226266813</v>
+        <v>372.7249226266812</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>405.5780829216038</v>
+        <v>405.5780829216036</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>507.1869034731984</v>
+        <v>507.1869034731981</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>497.1791837783035</v>
+        <v>497.1791837783033</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>486.1231138067801</v>
+        <v>486.1231138067798</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>372.7249226266813</v>
+        <v>372.7249226266812</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>405.5780829216038</v>
+        <v>405.5780829216035</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>507.1869034731984</v>
+        <v>507.1869034731981</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>497.1791837783035</v>
+        <v>497.1791837783032</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>486.1231138067801</v>
+        <v>486.1231138067798</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>48143.77129494142</v>
+        <v>48143.77129494141</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>38527.62012789738</v>
+        <v>38527.62012789736</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>29787.46480558971</v>
+        <v>29787.46480558969</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>27981.82746996802</v>
+        <v>27981.82746996801</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>28266.16132065955</v>
+        <v>28266.16132065954</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8313,46 +8313,46 @@
         <v>345.9823272812692</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>376.4783101559282</v>
+        <v>376.4783101559279</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>470.7968117441796</v>
+        <v>470.7968117441794</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>461.5071347179768</v>
+        <v>461.5071347179766</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>451.2443253722129</v>
+        <v>451.2443253722126</v>
       </c>
       <c r="Y79" s="148" t="n">
         <v>345.9823272812692</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>376.4783101559282</v>
+        <v>376.4783101559279</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>470.7968117441796</v>
+        <v>470.7968117441794</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>461.5071347179768</v>
+        <v>461.5071347179766</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>451.2443253722129</v>
+        <v>451.2443253722126</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>48143.77129494142</v>
+        <v>48143.77129494141</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>38527.62012789738</v>
+        <v>38527.62012789736</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>29787.46480558971</v>
+        <v>29787.46480558969</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>27981.82746996802</v>
+        <v>27981.82746996801</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>28266.16132065955</v>
+        <v>28266.16132065954</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8365,46 +8365,46 @@
         <v>958.3981191835306</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>924.8390126900514</v>
+        <v>924.8390126900513</v>
       </c>
       <c r="E80" s="156" t="n">
         <v>1050.873615488594</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>1128.494112488499</v>
+        <v>1128.494112488498</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>1160.334395335904</v>
+        <v>1160.334395335903</v>
       </c>
       <c r="H80" s="155" t="n">
         <v>958.3981191835308</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>924.8390126900514</v>
+        <v>924.8390126900512</v>
       </c>
       <c r="J80" s="156" t="n">
         <v>1050.873615488594</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>1128.494112488499</v>
+        <v>1128.494112488498</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>1160.334395335904</v>
+        <v>1160.334395335903</v>
       </c>
       <c r="M80" s="158" t="n">
         <v>61517.38851897914</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>44707.70003048893</v>
+        <v>44707.70003048892</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>36437.39687083825</v>
+        <v>36437.39687083824</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>39994.05765803606</v>
+        <v>39994.05765803604</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>43586.93904191582</v>
+        <v>43586.9390419158</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8415,46 +8415,46 @@
         <v>961.1054585032581</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>927.4515522739216</v>
+        <v>927.4515522739214</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1053.842185023873</v>
+        <v>1053.842185023872</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>1131.681948964455</v>
+        <v>1131.681948964454</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1163.612176113689</v>
+        <v>1163.612176113688</v>
       </c>
       <c r="Y80" s="155" t="n">
         <v>961.1054585032581</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>927.4515522739216</v>
+        <v>927.4515522739214</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>1053.842185023873</v>
+        <v>1053.842185023872</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>1131.681948964455</v>
+        <v>1131.681948964454</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>1163.612176113689</v>
+        <v>1163.612176113688</v>
       </c>
       <c r="AD80" s="158" t="n">
         <v>61517.38851897914</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>44707.70003048893</v>
+        <v>44707.70003048892</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>36437.39687083825</v>
+        <v>36437.39687083824</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>39994.05765803606</v>
+        <v>39994.05765803604</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>43586.93904191582</v>
+        <v>43586.9390419158</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8467,46 +8467,46 @@
         <v>567.1500737056224</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>580.7031768062943</v>
+        <v>580.7031768062941</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>709.0139037019845</v>
+        <v>709.0139037019842</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>741.1128156611846</v>
+        <v>741.1128156611843</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>750.7359628643726</v>
+        <v>750.7359628643723</v>
       </c>
       <c r="H81" s="161" t="n">
         <v>567.1500737056224</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>580.7031768062943</v>
+        <v>580.7031768062941</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>709.0139037019845</v>
+        <v>709.0139037019842</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>741.1128156611846</v>
+        <v>741.1128156611843</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>750.7359628643726</v>
+        <v>750.7359628643723</v>
       </c>
       <c r="M81" s="164" t="n">
         <v>109661.1598139206</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>83235.32015838631</v>
+        <v>83235.32015838628</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>66224.86167642796</v>
+        <v>66224.86167642793</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>67975.88512800408</v>
+        <v>67975.88512800405</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>71853.10036257537</v>
+        <v>71853.10036257534</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8517,46 +8517,46 @@
         <v>539.7829954045866</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>552.9051079765577</v>
+        <v>552.9051079765575</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>676.8269134276195</v>
+        <v>676.8269134276192</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>708.2903653597992</v>
+        <v>708.290365359799</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>717.821905003749</v>
+        <v>717.8219050037486</v>
       </c>
       <c r="Y81" s="161" t="n">
         <v>539.7829954045866</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>552.9051079765577</v>
+        <v>552.9051079765575</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>676.8269134276195</v>
+        <v>676.8269134276192</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>708.2903653597992</v>
+        <v>708.290365359799</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>717.821905003749</v>
+        <v>717.8219050037486</v>
       </c>
       <c r="AD81" s="164" t="n">
         <v>109661.1598139206</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>83235.32015838631</v>
+        <v>83235.32015838628</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>66224.86167642796</v>
+        <v>66224.86167642793</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>67975.88512800408</v>
+        <v>67975.88512800405</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>71853.10036257537</v>
+        <v>71853.10036257534</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8566,7 +8566,7 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>950.3649264551705</v>
+        <v>950.3649264551707</v>
       </c>
       <c r="D82" s="156" t="n">
         <v>1007.575621600445</v>
@@ -8581,7 +8581,7 @@
         <v>1220.266418397675</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>950.3649264551705</v>
+        <v>950.3649264551707</v>
       </c>
       <c r="I82" s="156" t="n">
         <v>1007.575621600445</v>
@@ -8596,13 +8596,13 @@
         <v>1220.266418397675</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>75282.73074080638</v>
+        <v>75282.73074080639</v>
       </c>
       <c r="N82" s="159" t="n">
         <v>77244.45953462097</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>82696.6410470899</v>
+        <v>82696.64104708991</v>
       </c>
       <c r="P82" s="159" t="n">
         <v>98531.36403832356</v>
@@ -8646,13 +8646,13 @@
         <v>1345.339468880054</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>75282.73074080638</v>
+        <v>75282.73074080639</v>
       </c>
       <c r="AE82" s="159" t="n">
         <v>77244.45953462097</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>82696.6410470899</v>
+        <v>82696.64104708991</v>
       </c>
       <c r="AG82" s="159" t="n">
         <v>98531.36403832356</v>
@@ -8671,37 +8671,37 @@
         <v>678.5206224313916</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>729.4565909415343</v>
+        <v>729.4565909415339</v>
       </c>
       <c r="E83" s="162" t="n">
         <v>895.2285584340768</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>958.2851200063084</v>
+        <v>958.2851200063081</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>973.7881860058081</v>
+        <v>973.7881860058079</v>
       </c>
       <c r="H83" s="161" t="n">
         <v>678.5206224313916</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>729.4565909415343</v>
+        <v>729.4565909415339</v>
       </c>
       <c r="J83" s="162" t="n">
         <v>895.2285584340768</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>958.2851200063084</v>
+        <v>958.2851200063081</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>973.7881860058081</v>
+        <v>973.7881860058079</v>
       </c>
       <c r="M83" s="164" t="n">
         <v>184943.8905547269</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>160479.7796930073</v>
+        <v>160479.7796930072</v>
       </c>
       <c r="O83" s="165" t="n">
         <v>148921.5027235179</v>
@@ -8721,37 +8721,37 @@
         <v>672.5036183020682</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>729.19427021718</v>
+        <v>729.1942702171798</v>
       </c>
       <c r="V83" s="162" t="n">
         <v>907.9996082123893</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>977.2737860526322</v>
+        <v>977.2737860526319</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>993.7571849598279</v>
+        <v>993.7571849598276</v>
       </c>
       <c r="Y83" s="161" t="n">
         <v>672.5036183020682</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>729.19427021718</v>
+        <v>729.1942702171798</v>
       </c>
       <c r="AA83" s="162" t="n">
         <v>907.9996082123893</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>977.2737860526322</v>
+        <v>977.2737860526319</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>993.7571849598279</v>
+        <v>993.7571849598276</v>
       </c>
       <c r="AD83" s="164" t="n">
         <v>184943.8905547269</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>160479.7796930073</v>
+        <v>160479.7796930072</v>
       </c>
       <c r="AF83" s="165" t="n">
         <v>148921.5027235179</v>
@@ -8773,37 +8773,37 @@
         <v>3081.646861394911</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>3268.632561966423</v>
+        <v>3268.632561966421</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>3485.042566386054</v>
+        <v>3485.042566386053</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>3695.587315909876</v>
+        <v>3695.587315909874</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>3909.331860076446</v>
+        <v>3909.331860076445</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>3081.646861394911</v>
+        <v>3081.64686139491</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>3268.632561966423</v>
+        <v>3268.632561966422</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>3485.042566386054</v>
+        <v>3485.042566386053</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>3695.587315909876</v>
+        <v>3695.587315909874</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>3909.331860076446</v>
+        <v>3909.331860076445</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>9559.286679843803</v>
+        <v>9559.286679843801</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>10380.55213069055</v>
+        <v>10380.55213069054</v>
       </c>
       <c r="O84" s="159" t="n">
         <v>11391.39721374559</v>
@@ -8820,40 +8820,40 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>845.5738339193352</v>
+        <v>845.5738339193351</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>896.8808859054208</v>
+        <v>896.8808859054204</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>956.2616798010513</v>
+        <v>956.2616798010509</v>
       </c>
       <c r="W84" s="156" t="n">
         <v>1014.03310497527</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>1072.682522581952</v>
+        <v>1072.682522581951</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>845.5738339193352</v>
+        <v>845.5738339193351</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>896.8808859054208</v>
+        <v>896.8808859054204</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>956.2616798010513</v>
+        <v>956.2616798010509</v>
       </c>
       <c r="AB84" s="156" t="n">
         <v>1014.03310497527</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>1072.682522581952</v>
+        <v>1072.682522581951</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>9559.286679843803</v>
+        <v>9559.286679843801</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>10380.55213069055</v>
+        <v>10380.55213069054</v>
       </c>
       <c r="AF84" s="159" t="n">
         <v>11391.39721374559</v>
@@ -8875,10 +8875,10 @@
         <v>705.5619269949739</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>765.5894079286403</v>
+        <v>765.5894079286401</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>945.1357589211229</v>
+        <v>945.1357589211228</v>
       </c>
       <c r="F85" s="180" t="n">
         <v>1009.828130235459</v>
@@ -8890,10 +8890,10 @@
         <v>705.5619269949739</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>765.5894079286403</v>
+        <v>765.5894079286401</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>945.1357589211229</v>
+        <v>945.1357589211228</v>
       </c>
       <c r="K85" s="180" t="n">
         <v>1009.828130235459</v>
@@ -8908,13 +8908,13 @@
         <v>170860.3318236978</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>160312.8999372635</v>
+        <v>160312.8999372634</v>
       </c>
       <c r="P85" s="183" t="n">
         <v>178830.4798477027</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>190843.7124838614</v>
+        <v>190843.7124838613</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8925,31 +8925,31 @@
         <v>679.3373047712596</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>737.5724080580662</v>
+        <v>737.572408058066</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>911.2676204293766</v>
+        <v>911.2676204293765</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>979.7211629059217</v>
+        <v>979.7211629059213</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>998.8786689528439</v>
+        <v>998.8786689528437</v>
       </c>
       <c r="Y85" s="185" t="n">
         <v>679.3373047712596</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>737.5724080580662</v>
+        <v>737.572408058066</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>911.2676204293766</v>
+        <v>911.2676204293765</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>979.7211629059217</v>
+        <v>979.7211629059213</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>998.8786689528439</v>
+        <v>998.8786689528437</v>
       </c>
       <c r="AD85" s="188" t="n">
         <v>194503.1772345707</v>
@@ -8958,13 +8958,13 @@
         <v>170860.3318236978</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>160312.8999372635</v>
+        <v>160312.8999372634</v>
       </c>
       <c r="AG85" s="189" t="n">
         <v>178830.4798477027</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>190843.7124838614</v>
+        <v>190843.7124838613</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9639,7 +9639,7 @@
         <v>79.21455079535443</v>
       </c>
       <c r="D93" s="80" t="n">
-        <v>76.66368447057597</v>
+        <v>76.66368447057596</v>
       </c>
       <c r="E93" s="80" t="n">
         <v>72.94608003974422</v>
@@ -9669,7 +9669,7 @@
         <v>79.21455079535443</v>
       </c>
       <c r="N93" s="80" t="n">
-        <v>76.66368447057597</v>
+        <v>76.66368447057596</v>
       </c>
       <c r="O93" s="80" t="n">
         <v>72.94608003974422</v>
@@ -9689,7 +9689,7 @@
         <v>71.85016006740376</v>
       </c>
       <c r="U93" s="80" t="n">
-        <v>69.53644179335365</v>
+        <v>69.53644179335363</v>
       </c>
       <c r="V93" s="80" t="n">
         <v>66.1644543145303</v>
@@ -9719,7 +9719,7 @@
         <v>71.85016006740376</v>
       </c>
       <c r="AE93" s="80" t="n">
-        <v>69.53644179335365</v>
+        <v>69.53644179335363</v>
       </c>
       <c r="AF93" s="80" t="n">
         <v>66.1644543145303</v>
@@ -10047,7 +10047,7 @@
         <v>175.9229630717332</v>
       </c>
       <c r="W96" s="136" t="n">
-        <v>182.5320168825168</v>
+        <v>182.5320168825169</v>
       </c>
       <c r="X96" s="137" t="n">
         <v>191.0579516969051</v>
@@ -10077,7 +10077,7 @@
         <v>175.9229630717332</v>
       </c>
       <c r="AG96" s="136" t="n">
-        <v>182.5320168825168</v>
+        <v>182.5320168825169</v>
       </c>
       <c r="AH96" s="137" t="n">
         <v>191.0579516969051</v>
